--- a/grid_search_results.xlsx
+++ b/grid_search_results.xlsx
@@ -497,23 +497,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>create_resnet</t>
+          <t>create_simple_feedforward_model</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.07946</v>
+        <v>1.971545219421387</v>
       </c>
       <c r="G2" t="n">
-        <v>0.11694809</v>
+        <v>0.3933083117008209</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1169480925578486</v>
+        <v>0.4290181363352095</v>
       </c>
       <c r="I2" t="n">
-        <v>0.125</v>
+        <v>0.390435583118871</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0261758118701007</v>
+        <v>0.3546323621057563</v>
       </c>
     </row>
     <row r="3">
@@ -533,23 +533,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>create_densenet</t>
+          <t>create_complex_feedforward_model</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.970000743865967</v>
+        <v>1.919785618782044</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3733583390712738</v>
+        <v>0.4033145606517792</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4033771106941838</v>
+        <v>0.4459036898061288</v>
       </c>
       <c r="I3" t="n">
-        <v>0.370130618092905</v>
+        <v>0.3988201899039053</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3317823162480547</v>
+        <v>0.382969591690952</v>
       </c>
     </row>
     <row r="4">
@@ -569,23 +569,23 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>create_simple_feedforward_model</t>
+          <t>create_residual_cnn_model</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.971545219421387</v>
+        <v>1.867265939712524</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3933083117008209</v>
+        <v>0.4686053693294525</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4290181363352095</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="I4" t="n">
-        <v>0.390435583118871</v>
+        <v>0.46636049705437</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3546323621057563</v>
+        <v>0.4614738988212316</v>
       </c>
     </row>
     <row r="5">
@@ -600,28 +600,28 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>compute_mel_spectrogram</t>
+          <t>compute_chromagram</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>create_complex_feedforward_model</t>
+          <t>create_simple_feedforward_model</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.919785618782044</v>
+        <v>2.022461414337158</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4033145606517792</v>
+        <v>0.3048780560493469</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4459036898061288</v>
+        <v>0.3433395872420263</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3988201899039053</v>
+        <v>0.3004649812397627</v>
       </c>
       <c r="J5" t="n">
-        <v>0.382969591690952</v>
+        <v>0.2738637944285306</v>
       </c>
     </row>
     <row r="6">
@@ -636,28 +636,28 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>compute_mel_spectrogram</t>
+          <t>compute_chromagram</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>create_residual_cnn_model</t>
+          <t>create_complex_feedforward_model</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.867265939712524</v>
+        <v>2.002831697463989</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4686053693294525</v>
+        <v>0.3033145666122436</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.3520950594121326</v>
       </c>
       <c r="I6" t="n">
-        <v>0.46636049705437</v>
+        <v>0.2982984834619578</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4614738988212316</v>
+        <v>0.281374550424401</v>
       </c>
     </row>
     <row r="7">
@@ -677,28 +677,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>create_resnet</t>
+          <t>create_residual_cnn_model</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.079461812973022</v>
+        <v>1.966695785522461</v>
       </c>
       <c r="G7" t="n">
-        <v>0.116948090493679</v>
+        <v>0.3826141357421875</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1169480925578486</v>
+        <v>0.4440275171982489</v>
       </c>
       <c r="I7" t="n">
-        <v>0.125</v>
+        <v>0.3778103269484027</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0261758118701007</v>
+        <v>0.3599958064843465</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B8" t="n">
         <v>256</v>
@@ -708,33 +708,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>compute_chromagram</t>
+          <t>compute_mel_spectrogram</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>create_densenet</t>
+          <t>create_simple_feedforward_model</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.001558780670166</v>
+        <v>1.996831297874451</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3388367593288421</v>
+        <v>0.3550135493278503</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3871169480925578</v>
+        <v>0.3595997498436523</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3336180660217438</v>
+        <v>0.3495931345803309</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3090711374771979</v>
+        <v>0.2894815157161763</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B9" t="n">
         <v>256</v>
@@ -744,33 +744,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>compute_chromagram</t>
+          <t>compute_mel_spectrogram</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>create_simple_feedforward_model</t>
+          <t>create_complex_feedforward_model</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.022461414337158</v>
+        <v>1.964112877845764</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3048780560493469</v>
+        <v>0.3771106898784637</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3433395872420263</v>
+        <v>0.3952470293933708</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3004649812397627</v>
+        <v>0.3731586999005525</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2738637944285306</v>
+        <v>0.351854108865464</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B10" t="n">
         <v>256</v>
@@ -780,33 +780,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>compute_chromagram</t>
+          <t>compute_mel_spectrogram</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>create_complex_feedforward_model</t>
+          <t>create_residual_cnn_model</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.002831697463989</v>
+        <v>1.906096935272217</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3033145666122436</v>
+        <v>0.4621638655662536</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3520950594121326</v>
+        <v>0.4702939337085678</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2982984834619578</v>
+        <v>0.4613167536249931</v>
       </c>
       <c r="J10" t="n">
-        <v>0.281374550424401</v>
+        <v>0.4565517719538472</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B11" t="n">
         <v>256</v>
@@ -821,23 +821,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>create_residual_cnn_model</t>
+          <t>create_simple_feedforward_model</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.966695785522461</v>
+        <v>2.046647548675537</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3826141357421875</v>
+        <v>0.2324369400739669</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4440275171982489</v>
+        <v>0.2395247029393371</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3778103269484027</v>
+        <v>0.2343709404977284</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3599958064843465</v>
+        <v>0.1796281700472579</v>
       </c>
     </row>
     <row r="12">
@@ -852,28 +852,28 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>compute_mel_spectrogram</t>
+          <t>compute_chromagram</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>create_resnet</t>
+          <t>create_complex_feedforward_model</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.059154987335205</v>
+        <v>2.032142162322998</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2165936976671219</v>
+        <v>0.2580779790878296</v>
       </c>
       <c r="H12" t="n">
-        <v>0.215134459036898</v>
+        <v>0.257661038148843</v>
       </c>
       <c r="I12" t="n">
-        <v>0.207568071887814</v>
+        <v>0.2552167135083931</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1506249834740479</v>
+        <v>0.2290172468152752</v>
       </c>
     </row>
     <row r="13">
@@ -888,33 +888,33 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>compute_mel_spectrogram</t>
+          <t>compute_chromagram</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>create_densenet</t>
+          <t>create_residual_cnn_model</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.9984450340271</v>
+        <v>1.974793791770935</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3385449349880218</v>
+        <v>0.3873254060745239</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3545966228893058</v>
+        <v>0.4015009380863039</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3356183906566771</v>
+        <v>0.3820675027708187</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3059747505331719</v>
+        <v>0.3619966564136959</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B14" t="n">
         <v>256</v>
@@ -924,33 +924,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>compute_mel_spectrogram</t>
+          <t>compute_spectral_features</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>create_simple_feedforward_model</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1.996831297874451</v>
-      </c>
+          <t>create_random_forest</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.3550135493278503</v>
+        <v>0.4686053693294525</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3595997498436523</v>
+        <v>0.5190744215134458</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3495931345803309</v>
+        <v>0.4671868184946312</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2894815157161763</v>
+        <v>0.4587112981141336</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B15" t="n">
         <v>256</v>
@@ -960,33 +958,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>compute_mel_spectrogram</t>
+          <t>compute_spectral_features</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>create_complex_feedforward_model</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1.964112877845764</v>
-      </c>
+          <t>create_svm</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.3771106898784637</v>
+        <v>0.4822388887405395</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3952470293933708</v>
+        <v>0.5328330206378987</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3731586999005525</v>
+        <v>0.4811712019228243</v>
       </c>
       <c r="J15" t="n">
-        <v>0.351854108865464</v>
+        <v>0.4753987405364374</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B16" t="n">
         <v>256</v>
@@ -996,33 +992,33 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>compute_mel_spectrogram</t>
+          <t>compute_spectral_features</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>create_residual_cnn_model</t>
+          <t>create_simple_feedforward_model</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.906096935272217</v>
+        <v>1.894526362419128</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4621638655662536</v>
+        <v>0.4618511497974396</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4702939337085678</v>
+        <v>0.5034396497811132</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4613167536249931</v>
+        <v>0.4603169254290079</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4565517719538472</v>
+        <v>0.45007181422777</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B17" t="n">
         <v>256</v>
@@ -1032,33 +1028,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>compute_chromagram</t>
+          <t>compute_tempo_features</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>create_resnet</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>2.07939076423645</v>
-      </c>
+          <t>create_random_forest</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>0.1173650175333023</v>
+        <v>0.1872420310974121</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1175734834271419</v>
+        <v>0.2132582864290181</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1247783687943262</v>
+        <v>0.1887724605873134</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0262789395070948</v>
+        <v>0.1781450995588556</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B18" t="n">
         <v>256</v>
@@ -1068,33 +1062,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>compute_chromagram</t>
+          <t>compute_tempo_features</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>create_densenet</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>2.00006103515625</v>
-      </c>
+          <t>create_svm</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>0.3352095186710357</v>
+        <v>0.2029393315315246</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3520950594121326</v>
+        <v>0.2295184490306441</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3292690066186869</v>
+        <v>0.2048569840670544</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2988938494767903</v>
+        <v>0.1837718087794599</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B19" t="n">
         <v>256</v>
@@ -1104,7 +1096,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>compute_chromagram</t>
+          <t>compute_tempo_features</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1113,19 +1105,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.046647548675537</v>
+        <v>2.064284324645996</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2324369400739669</v>
+        <v>0.2125703543424606</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2395247029393371</v>
+        <v>0.2407754846779237</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2343709404977284</v>
+        <v>0.2146782159772247</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1796281700472579</v>
+        <v>0.1937778514140199</v>
       </c>
     </row>
     <row r="20">
@@ -1140,28 +1132,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>compute_chromagram</t>
+          <t>compute_spectral_features</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>create_complex_feedforward_model</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>2.032142162322998</v>
-      </c>
+          <t>create_random_forest</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>0.2580779790878296</v>
+        <v>0.480925589799881</v>
       </c>
       <c r="H20" t="n">
-        <v>0.257661038148843</v>
+        <v>0.4921826141338336</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2552167135083931</v>
+        <v>0.4791952065444598</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2290172468152752</v>
+        <v>0.4724589646375537</v>
       </c>
     </row>
     <row r="21">
@@ -1176,33 +1166,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>compute_chromagram</t>
+          <t>compute_spectral_features</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>create_residual_cnn_model</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1.974793791770935</v>
-      </c>
+          <t>create_svm</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>0.3873254060745239</v>
+        <v>0.501354992389679</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4015009380863039</v>
+        <v>0.5222013758599124</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3820675027708187</v>
+        <v>0.5000155841751037</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3619966564136959</v>
+        <v>0.4955177511817901</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B22" t="n">
         <v>256</v>
@@ -1217,26 +1205,28 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>create_random_forest</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>create_simple_feedforward_model</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.883875727653504</v>
+      </c>
       <c r="G22" t="n">
-        <v>0.4686053693294525</v>
+        <v>0.482593297958374</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5190744215134458</v>
+        <v>0.5021888680425266</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4671868184946312</v>
+        <v>0.4800081042920984</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4587112981141336</v>
+        <v>0.464880710950955</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B23" t="n">
         <v>256</v>
@@ -1246,31 +1236,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>compute_spectral_features</t>
+          <t>compute_tempo_features</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>create_svm</t>
+          <t>create_random_forest</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
-        <v>0.4822388887405395</v>
+        <v>0.1999166160821914</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5328330206378987</v>
+        <v>0.2063789868667917</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4811712019228243</v>
+        <v>0.2008600514502483</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4753987405364374</v>
+        <v>0.1971727076624944</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B24" t="n">
         <v>256</v>
@@ -1280,33 +1270,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>compute_spectral_features</t>
+          <t>compute_tempo_features</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>create_simple_feedforward_model</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1.894526362419128</v>
-      </c>
+          <t>create_svm</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0.4618511497974396</v>
+        <v>0.2088805437088012</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5034396497811132</v>
+        <v>0.2176360225140713</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4603169254290079</v>
+        <v>0.2123325892764204</v>
       </c>
       <c r="J24" t="n">
-        <v>0.45007181422777</v>
+        <v>0.2016404387101515</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B25" t="n">
         <v>256</v>
@@ -1321,21 +1309,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>create_random_forest</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>create_simple_feedforward_model</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.0594162940979</v>
+      </c>
       <c r="G25" t="n">
-        <v>0.1872420310974121</v>
+        <v>0.2257661074399948</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2132582864290181</v>
+        <v>0.2351469668542839</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1887724605873134</v>
+        <v>0.2269128812888472</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1781450995588556</v>
+        <v>0.2019486546097258</v>
       </c>
     </row>
     <row r="26">
@@ -1350,26 +1340,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>compute_tempo_features</t>
+          <t>compute_mel_spectrogram</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>create_svm</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>create_resnet</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3.777788400650024</v>
+      </c>
       <c r="G26" t="n">
-        <v>0.2029393315315246</v>
+        <v>0.3020637929439545</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2295184490306441</v>
+        <v>0.3577235772357724</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2048569840670544</v>
+        <v>0.3040733673781706</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1837718087794599</v>
+        <v>0.3096218571937767</v>
       </c>
     </row>
     <row r="27">
@@ -1384,33 +1376,33 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>compute_tempo_features</t>
+          <t>compute_mel_spectrogram</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>create_simple_feedforward_model</t>
+          <t>create_densenet</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.064284324645996</v>
+        <v>1.437423944473267</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2125703543424606</v>
+        <v>0.5029393434524536</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2407754846779237</v>
+        <v>0.5703564727954972</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2146782159772247</v>
+        <v>0.5005090457382182</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1937778514140199</v>
+        <v>0.4942623033203945</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B28" t="n">
         <v>256</v>
@@ -1420,31 +1412,33 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>compute_spectral_features</t>
+          <t>compute_chromagram</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>create_random_forest</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>create_resnet</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>5.755733966827393</v>
+      </c>
       <c r="G28" t="n">
-        <v>0.480925589799881</v>
+        <v>0.118824265897274</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4921826141338336</v>
+        <v>0.1188242651657286</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4791952065444598</v>
+        <v>0.125</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4724589646375537</v>
+        <v>0.026554114490161</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B29" t="n">
         <v>256</v>
@@ -1454,26 +1448,28 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>compute_spectral_features</t>
+          <t>compute_chromagram</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>create_svm</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>create_densenet</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.807841062545776</v>
+      </c>
       <c r="G29" t="n">
-        <v>0.501354992389679</v>
+        <v>0.3227016925811768</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5222013758599124</v>
+        <v>0.3533458411507192</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5000155841751037</v>
+        <v>0.3155567756972962</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4955177511817901</v>
+        <v>0.2854807745683501</v>
       </c>
     </row>
     <row r="30">
@@ -1488,28 +1484,28 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>compute_spectral_features</t>
+          <t>compute_mel_spectrogram</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>create_simple_feedforward_model</t>
+          <t>create_resnet</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.883875727653504</v>
+        <v>4.233937740325928</v>
       </c>
       <c r="G30" t="n">
-        <v>0.482593297958374</v>
+        <v>0.2951844930648804</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5021888680425266</v>
+        <v>0.3108192620387742</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4800081042920984</v>
+        <v>0.2949105558923061</v>
       </c>
       <c r="J30" t="n">
-        <v>0.464880710950955</v>
+        <v>0.2807076416877481</v>
       </c>
     </row>
     <row r="31">
@@ -1524,26 +1520,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>compute_tempo_features</t>
+          <t>compute_mel_spectrogram</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>create_random_forest</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>create_densenet</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.397363185882568</v>
+      </c>
       <c r="G31" t="n">
-        <v>0.1999166160821914</v>
+        <v>0.5067750811576843</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2063789868667917</v>
+        <v>0.5309568480300187</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2008600514502483</v>
+        <v>0.5032681806398384</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1971727076624944</v>
+        <v>0.496573557350646</v>
       </c>
     </row>
     <row r="32">
@@ -1558,26 +1556,28 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>compute_tempo_features</t>
+          <t>compute_chromagram</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>create_svm</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>create_resnet</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>7.828051567077637</v>
+      </c>
       <c r="G32" t="n">
-        <v>0.2088805437088012</v>
+        <v>0.1250781714916229</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2176360225140713</v>
+        <v>0.1250781738586617</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2123325892764204</v>
+        <v>0.125</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2016404387101515</v>
+        <v>0.02779321845469705</v>
       </c>
     </row>
     <row r="33">
@@ -1592,28 +1592,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>compute_tempo_features</t>
+          <t>compute_chromagram</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>create_simple_feedforward_model</t>
+          <t>create_densenet</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.0594162940979</v>
+        <v>1.986945986747742</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2257661074399948</v>
+        <v>0.2787158787250519</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2351469668542839</v>
+        <v>0.2908067542213884</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2269128812888472</v>
+        <v>0.263854332465194</v>
       </c>
       <c r="J33" t="n">
-        <v>0.2019486546097258</v>
+        <v>0.1894088346558899</v>
       </c>
     </row>
   </sheetData>

--- a/grid_search_results.xlsx
+++ b/grid_search_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,16 +1352,16 @@
         <v>3.777788400650024</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3020637929439545</v>
+        <v>0.3020637929439544</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3577235772357724</v>
+        <v>0.3577235772357723</v>
       </c>
       <c r="I26" t="n">
         <v>0.3040733673781706</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3096218571937767</v>
+        <v>0.3096218571937766</v>
       </c>
     </row>
     <row r="27">
@@ -1427,7 +1427,7 @@
         <v>0.118824265897274</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1188242651657286</v>
+        <v>0.1188242651657285</v>
       </c>
       <c r="I28" t="n">
         <v>0.125</v>
@@ -1460,7 +1460,7 @@
         <v>1.807841062545776</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3227016925811768</v>
+        <v>0.3227016925811767</v>
       </c>
       <c r="H29" t="n">
         <v>0.3533458411507192</v>
@@ -1496,7 +1496,7 @@
         <v>4.233937740325928</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2951844930648804</v>
+        <v>0.2951844930648803</v>
       </c>
       <c r="H30" t="n">
         <v>0.3108192620387742</v>
@@ -1541,7 +1541,7 @@
         <v>0.5032681806398384</v>
       </c>
       <c r="J31" t="n">
-        <v>0.496573557350646</v>
+        <v>0.4965735573506459</v>
       </c>
     </row>
     <row r="32">
@@ -1571,13 +1571,13 @@
         <v>0.1250781714916229</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1250781738586617</v>
+        <v>0.1250781738586616</v>
       </c>
       <c r="I32" t="n">
         <v>0.125</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02779321845469705</v>
+        <v>0.027793218454697</v>
       </c>
     </row>
     <row r="33">
@@ -1607,13 +1607,157 @@
         <v>0.2787158787250519</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2908067542213884</v>
+        <v>0.2908067542213883</v>
       </c>
       <c r="I33" t="n">
-        <v>0.263854332465194</v>
+        <v>0.2638543324651939</v>
       </c>
       <c r="J33" t="n">
         <v>0.1894088346558899</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B34" t="n">
+        <v>256</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>compute_spectral_features</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>create_complex_feedforward_model</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.492031693458557</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.4706066250801086</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.5215759849906192</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.4695050097429759</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.464179057488023</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>10</v>
+      </c>
+      <c r="B35" t="n">
+        <v>256</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>compute_tempo_features</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>create_complex_feedforward_model</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2.024476528167725</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.2142589092254639</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2501563477173233</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.2164241155943901</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.1980173895602941</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" t="n">
+        <v>256</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>compute_spectral_features</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>create_complex_feedforward_model</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.468343257904053</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.4869710206985474</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.4978111319574734</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.4853510104615391</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.472234490943642</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" t="n">
+        <v>256</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>compute_tempo_features</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>create_complex_feedforward_model</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.003098487854004</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.2311861515045166</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2407754846779237</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2322470102409525</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.2173996394397385</v>
       </c>
     </row>
   </sheetData>
